--- a/output/full_scan/batch_seq8_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7712</v>
+        <v>7610</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1026.453596691758</v>
+        <v>1253.955285252275</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>184.5</v>
+        <v>2315</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.47078622758102</v>
+        <v>80.18180781078991</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.1684267107694</v>
+        <v>55.88915123919838</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.064445966966009</v>
+        <v>4.218784804807338</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.282894350426552</v>
+        <v>29.44208706220428</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7610</v>
+        <v>7712</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>937.032531307098</v>
+        <v>1226.453596691758</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2315</v>
+        <v>184.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>80.18180781036268</v>
+        <v>67.47078615945651</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>55.88915118492876</v>
+        <v>22.16842672535109</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.591308653341814</v>
+        <v>3.064445966966009</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>29.44208706228048</v>
+        <v>1.282894352525315</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6949</v>
+        <v>7734</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>844.6773886811707</v>
+        <v>987.9005258489774</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>911</v>
+        <v>3615</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>77.2713268367536</v>
+        <v>57.5798119358565</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.86479833355272</v>
+        <v>22.31220982094863</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.067738868117068</v>
+        <v>1.034590332292282</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>27.44991224320471</v>
+        <v>10.95216455570819</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6901</v>
+        <v>6862</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>787.1329464591848</v>
+        <v>947.036135095865</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.55</v>
+        <v>227</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.52038522823523</v>
+        <v>61.97230924141576</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.37127207313711</v>
+        <v>24.06958126829194</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.034459175954008</v>
+        <v>0.5108152053820165</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.208285048123557</v>
+        <v>1.525769846645995</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6919</v>
+        <v>7715</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>781.9317305910412</v>
+        <v>907.8519840893284</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>109</v>
+        <v>32.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.83951081791626</v>
+        <v>68.68571803996902</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.54654657894008</v>
+        <v>28.00765992882794</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.250969212672749</v>
+        <v>4.385198408932845</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.44259146011671</v>
+        <v>0.4463278126649261</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>752.8572624005737</v>
+        <v>887.8572624005737</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>22.3</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.14992109099774</v>
+        <v>66.14992095798303</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32.90052018296122</v>
+        <v>32.90052009897639</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.8857262400573707</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3362059022599766</v>
+        <v>0.3362059025461689</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6907</v>
+        <v>6859</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>742.5878054950049</v>
+        <v>854.291958521682</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>135.5</v>
+        <v>139</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>51.6381230859709</v>
+        <v>66.54102514351862</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.27335807284791</v>
+        <v>27.76002931516605</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3790718215480017</v>
+        <v>4.029195852168194</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-1.014432258892294</v>
+        <v>0.8190734170096468</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7715</v>
+        <v>6962</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>737.8519840893284</v>
+        <v>844.9932330493197</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32.4</v>
+        <v>38.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.68571808935002</v>
+        <v>58.65203025088893</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.00765992882794</v>
+        <v>14.90328031894285</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.385198408932845</v>
+        <v>1.225427755355804</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4463278125695322</v>
+        <v>0.1916046807249228</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8044</v>
+        <v>7795</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>729.186093263623</v>
+        <v>833.227694511472</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.15</v>
+        <v>410</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.94769990217181</v>
+        <v>57.14056071202359</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.31527377446195</v>
+        <v>13.19480516261392</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.390114316782621</v>
+        <v>0.7919784478477986</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.2599045162753486</v>
+        <v>2.177973659795845</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6862</v>
+        <v>6944</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>727.0361350958651</v>
+        <v>768.5683348281804</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>227</v>
+        <v>1045</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.97230930191861</v>
+        <v>67.96657837597643</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.06958134757664</v>
+        <v>16.03118528692688</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5108152053820165</v>
+        <v>0.8299085713804519</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.525769844547252</v>
+        <v>11.42030742116617</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6859</v>
+        <v>7788</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>714.291958521682</v>
+        <v>758.1350586335629</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>139</v>
+        <v>292</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.54102519397124</v>
+        <v>75.22909112239952</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.76002930545442</v>
+        <v>42.79815400685084</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.029195852168194</v>
+        <v>1.167671524725213</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8190734159602795</v>
+        <v>5.99656325006756</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7734</v>
+        <v>6907</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>702.9005258489774</v>
+        <v>742.5878054950049</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3615</v>
+        <v>135.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.57981193682993</v>
+        <v>51.6381230859709</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.31220986145189</v>
+        <v>26.27335807284791</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.034590332292282</v>
+        <v>0.3790718215480017</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>10.95216454922102</v>
+        <v>-1.014432258892294</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7788</v>
+        <v>8032</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>698.1350586335629</v>
+        <v>740.7355384641152</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>292</v>
+        <v>47.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>75.22909149757272</v>
+        <v>64.44837833367268</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>42.79815411872968</v>
+        <v>29.05620439757024</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.167671524725213</v>
+        <v>0.8181130490896236</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>5.99656322001745</v>
+        <v>0.1096101460042295</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7827</v>
+        <v>8028</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>694.7867890035916</v>
+        <v>733.7135128963364</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>164.5</v>
+        <v>311.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.60546667841415</v>
+        <v>54.61450157490888</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.67880571143168</v>
+        <v>41.25572473915537</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4099837663020374</v>
+        <v>0.7446180494833534</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.944323625013518</v>
+        <v>-5.252989334383123</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7722</v>
+        <v>6922</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>692.5074734046847</v>
+        <v>669.1119173573642</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>328</v>
+        <v>186</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.07711008396815</v>
+        <v>48.86222419665238</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>37.02612462088067</v>
+        <v>21.84170365551821</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8867378661926932</v>
+        <v>0.3588929340142003</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.110925333738905</v>
+        <v>-1.813926003701213</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8043</v>
+        <v>8016</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>671.5462315557384</v>
+        <v>654.4589501941159</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>226.5</v>
+        <v>300.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>79.43040147140103</v>
+        <v>59.05604690447676</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44.82124789726549</v>
+        <v>41.13419394963103</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.364997864833249</v>
+        <v>1.140336946547016</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4.560006579556795</v>
+        <v>-2.875145279984213</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8028</v>
+        <v>7751</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>658.7114797457691</v>
+        <v>615.4893416527729</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>311.5</v>
+        <v>1485</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.61450159246629</v>
+        <v>43.73879081610948</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41.25572479419147</v>
+        <v>17.76029034641975</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.744414734426625</v>
+        <v>0.7203721557105931</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-5.252989334860111</v>
+        <v>2.604911588445816</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8016</v>
+        <v>6894</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>654.4492235725742</v>
+        <v>600.2503068362007</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>300.5</v>
+        <v>374.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>59.05604686239806</v>
+        <v>54.54489481769449</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>41.1341939366534</v>
+        <v>22.51425030627797</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.139512157319592</v>
+        <v>0.6439822772194413</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-2.875145280175014</v>
+        <v>-2.007963300485517</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6922</v>
+        <v>8040</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>649.1119173573642</v>
+        <v>599.5371487623396</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>186</v>
+        <v>94.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>48.86222421951992</v>
+        <v>49.06764876268207</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.84170365198748</v>
+        <v>33.27642056745299</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3588929340142003</v>
+        <v>0.2991987573095594</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.81392600503675</v>
+        <v>-2.543443883278947</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6870</v>
+        <v>6928</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>637.7234640164453</v>
+        <v>597.7321188504669</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>285.5</v>
+        <v>47.95</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.86224374273813</v>
+        <v>55.56043439497374</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.23350784960495</v>
+        <v>18.65388862148918</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.507219104700247</v>
+        <v>0.5807704309836691</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-3.417477448428688</v>
+        <v>0.3077237068065564</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6944</v>
+        <v>7769</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>628.5683348281804</v>
+        <v>577.3663924961251</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1045</v>
+        <v>6975</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>67.96657837673712</v>
+        <v>49.92241458741501</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.03118528032424</v>
+        <v>26.1350989544269</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8299085713804519</v>
+        <v>1.756544484813861</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>11.42030742068903</v>
+        <v>-111.8347939315777</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6957</v>
+        <v>7786</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>610.7595085314617</v>
+        <v>569.9334135486423</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>189.5</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.50327988702102</v>
+        <v>56.89132874301954</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.28546011739444</v>
+        <v>21.744046685636</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3971731357373318</v>
+        <v>0.565886563057089</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.231667354601682</v>
+        <v>1.686091075600813</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8032</v>
+        <v>6899</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>600.7355384641153</v>
+        <v>565.7639725880447</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>47.6</v>
+        <v>60.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>64.4483782286604</v>
+        <v>49.73096334190152</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.05620448540206</v>
+        <v>21.81735437142484</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8181130490896236</v>
+        <v>0.2232148690362529</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1096101457466527</v>
+        <v>-0.5246901299096405</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8040</v>
+        <v>7822</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>579.5371487623396</v>
+        <v>557.5610880879431</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>94.8</v>
+        <v>1165</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.06764880299279</v>
+        <v>52.21032986535594</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.27642049304916</v>
+        <v>15.27901928846354</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2991987573095594</v>
+        <v>0.6843316997777271</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-2.543443883813178</v>
+        <v>22.02124796145895</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7769</v>
+        <v>7749</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>577.2325857223623</v>
+        <v>556.8429773371901</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>6975</v>
+        <v>484.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.92241458946361</v>
+        <v>49.23088328915198</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.13509898168336</v>
+        <v>24.57667571278461</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.741021831160881</v>
+        <v>0.5053467570796943</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-111.8347939350117</v>
+        <v>-2.676221013404523</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7749</v>
+        <v>7772</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>556.8429773371901</v>
+        <v>528.625633689105</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>484.5</v>
+        <v>144</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.23088328915198</v>
+        <v>44.1685213886233</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24.57667571278461</v>
+        <v>10.22435008202764</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5053467570796943</v>
+        <v>0.3020997329100194</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-2.676221013404523</v>
+        <v>-0.8611997538275933</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6997</v>
+        <v>6996</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>551.5711108272301</v>
+        <v>519.9140229928366</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.95485876514901</v>
+        <v>52.97868774095526</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9.024951409684062</v>
+        <v>26.11084057336648</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7031895506032781</v>
+        <v>0.365468008158648</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2136492442474979</v>
+        <v>-0.6636070429471093</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7795</v>
+        <v>7631</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>543.2276945114721</v>
+        <v>518.6204920518406</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>410</v>
+        <v>131.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.14056071363559</v>
+        <v>52.99289637569444</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13.19480515160036</v>
+        <v>11.38796907973604</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7919784478477986</v>
+        <v>0.8190607558399428</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.177973659414288</v>
+        <v>2.383752150672917</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6934</v>
+        <v>6909</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>542.5163829342484</v>
+        <v>517.6584620629204</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>71.3</v>
+        <v>50.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.29458448261899</v>
+        <v>52.73954754873523</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.75840066509496</v>
+        <v>19.38865011854004</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.725741867851815</v>
+        <v>0.7663678731288543</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0976017676478364</v>
+        <v>0.2044289075414611</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7799</v>
+        <v>8038</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>534.54949831472</v>
+        <v>494.0488199881506</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>362</v>
+        <v>40.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.43506637680084</v>
+        <v>47.18662902348751</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.37383409762132</v>
+        <v>8.096168990550082</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.720813624847022</v>
+        <v>0.7366652280783546</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>2.99439658167373</v>
+        <v>-0.0006591264180267</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6962</v>
+        <v>7768</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>519.9932330493198</v>
+        <v>492.4421157828301</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>38.9</v>
+        <v>373</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.65203024429408</v>
+        <v>44.14416201608335</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.90328031088888</v>
+        <v>16.53369312403196</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.225427755355804</v>
+        <v>0.417429141261481</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1916046806199857</v>
+        <v>-2.669767958587202</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7631</v>
+        <v>7792</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>518.6204920518408</v>
+        <v>488.5625833464821</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>131.5</v>
+        <v>261</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.99289638399468</v>
+        <v>41.09836395617206</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.38796908414224</v>
+        <v>22.59391806353022</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8190607558399428</v>
+        <v>0.5250550882829239</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.383752150386715</v>
+        <v>0.413962657483534</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6996</v>
+        <v>7556</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>499.9140229928366</v>
+        <v>480.9658022500324</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>194</v>
+        <v>275</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>52.97868772880275</v>
+        <v>50.43781068077278</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.11084057336648</v>
+        <v>14.35387541298493</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.365468008158648</v>
+        <v>0.4499932620181174</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.6636070430425018</v>
+        <v>-1.187139003385701</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7721</v>
+        <v>7711</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>497.5897910431749</v>
+        <v>468.8680222571436</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>364.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.22137650209764</v>
+        <v>46.54543546892593</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.22118574541782</v>
+        <v>15.20476050171334</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6095267323383532</v>
+        <v>0.3195542206711939</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.2197653521970826</v>
+        <v>-3.400538332695817</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6931</v>
+        <v>8046</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>495.3043685114233</v>
+        <v>453.2247808941766</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>40.8</v>
+        <v>874</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>40.5197789557449</v>
+        <v>51.81213536549598</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.33506425175317</v>
+        <v>15.56943907480537</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9980024173154238</v>
+        <v>0.9977370179756412</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.311145508083392</v>
+        <v>-1.925930552324632</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7768</v>
+        <v>6921</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>492.44211578283</v>
+        <v>448.767736203702</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>373</v>
+        <v>71.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>44.14416204442325</v>
+        <v>41.56921731537675</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.53369315073811</v>
+        <v>27.52633904956159</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.417429141261481</v>
+        <v>1.557288776412477</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.669767958968778</v>
+        <v>0.068102381376343</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7792</v>
+        <v>6994</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>488.5625833464821</v>
+        <v>431.1890524576613</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>261</v>
+        <v>53.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>41.09836396410363</v>
+        <v>33.87052383644441</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.59391806164789</v>
+        <v>18.24864514962118</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5250550882829239</v>
+        <v>1.917830044310564</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.413962657578935</v>
+        <v>-0.5431876939490561</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6894</v>
+        <v>6971</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>485.2503068362007</v>
+        <v>424.7531116606714</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>374.5</v>
+        <v>27.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.54489481769449</v>
+        <v>55.79483099667572</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.51425035155156</v>
+        <v>18.66283544547555</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6439822772194413</v>
+        <v>6.858083079349517</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-2.007963301057947</v>
+        <v>0.1123674090439286</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7556</v>
+        <v>8039</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>480.9658022500324</v>
+        <v>422.5820057180303</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>275</v>
+        <v>145.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.43781075976749</v>
+        <v>52.23409039173137</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.35387545459056</v>
+        <v>22.53427725444031</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4499932620181174</v>
+        <v>0.3415962345519952</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.187139005102865</v>
+        <v>-0.1447782291343317</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7711</v>
+        <v>7730</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>468.8680222571436</v>
+        <v>413.0968385043983</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>364.5</v>
+        <v>180.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.54543551147356</v>
+        <v>45.29952967867194</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.20476045115377</v>
+        <v>18.23491138656478</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3195542206711939</v>
+        <v>0.922300514567449</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.400538333745158</v>
+        <v>-3.432634284979499</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7760</v>
+        <v>6983</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>464.7067073967402</v>
+        <v>410.3143312976839</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>33.6</v>
+        <v>371</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.3986626747453</v>
+        <v>49.12801635364296</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>51.07186398539822</v>
+        <v>14.79598920336904</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.239237223997006</v>
+        <v>0.5544578149974652</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2831274418660925</v>
+        <v>1.203204793319742</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7786</v>
+        <v>6937</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>459.9334135486425</v>
+        <v>373.6870141332407</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>130</v>
+        <v>279.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.8913286356981</v>
+        <v>45.67326867895551</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.74404668668107</v>
+        <v>14.43951114899719</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.565886563057089</v>
+        <v>0.6385490452278444</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.686091075696213</v>
+        <v>-2.066922559587018</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6965</v>
+        <v>6877</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>457.529040740807</v>
+        <v>367.0677234485899</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>82</v>
+        <v>129.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.88810631575078</v>
+        <v>33.95130760733625</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.91330548150038</v>
+        <v>22.13398511705011</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.668623395266623</v>
+        <v>0.4374758432667606</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.3657690337443085</v>
+        <v>-2.819663292358374</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6899</v>
+        <v>6903</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>455.7639725880448</v>
+        <v>348.2842869429546</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>60.8</v>
+        <v>393</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.73096334637777</v>
+        <v>50.35929659966996</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.81735437999576</v>
+        <v>15.23688062210877</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2232148690362529</v>
+        <v>0.3724515995218305</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.524690129928711</v>
+        <v>-1.279158187281936</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6925</v>
+        <v>6967</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>452.8038711250216</v>
+        <v>346.5894321621794</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>63.7</v>
+        <v>71.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.36348146388184</v>
+        <v>48.97001517402723</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.56178228224165</v>
+        <v>8.928712743276755</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2462700124787925</v>
+        <v>0.2602919316211082</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.5308472313481407</v>
+        <v>0.1683006971226828</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6906</v>
+        <v>7810</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>442.7557583140691</v>
+        <v>343.8060314074121</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>208</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.83922898235193</v>
+        <v>42.50703540058263</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>28.87745182654209</v>
+        <v>16.22151006662083</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6413431135715212</v>
+        <v>0.2790767346079177</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.135554960965682</v>
+        <v>-1.527069311648167</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7780</v>
+        <v>7842</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>441.96783481067</v>
+        <v>341.6545141031607</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>19.2</v>
+        <v>101</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>57.75741554213405</v>
+        <v>33.88043535380196</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.59962240071567</v>
+        <v>28.1770743341323</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.330622072181422</v>
+        <v>0.2151725515145541</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2412769929172908</v>
+        <v>0.5934244629452268</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6928</v>
+        <v>7744</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>437.732118850469</v>
+        <v>333.4268303378885</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>47.95</v>
+        <v>483</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.56043438584975</v>
+        <v>46.7450465378931</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.65388860466675</v>
+        <v>13.33824504622382</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5807704309836691</v>
+        <v>0.2567902004705649</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.3077237065012861</v>
+        <v>1.251186721463942</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7732</v>
+        <v>6913</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>434.2812256037837</v>
+        <v>329.8392309500776</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.93558381698674</v>
+        <v>44.39803875227739</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.28765613439564</v>
+        <v>17.66333668889722</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.749934377460845</v>
+        <v>0.3239869523071693</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.309985943411244</v>
+        <v>-1.38129181853682</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6902</v>
+        <v>6855</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>431.4450953227969</v>
+        <v>311.6636533119414</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.18357705714446</v>
+        <v>19.43593864093283</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>30.6698423107172</v>
+        <v>18.42662956809367</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3755523079881189</v>
+        <v>0.0002117119024431</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-2.905209917379972</v>
+        <v>-9.039665618099562</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6921</v>
+        <v>7820</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>428.767736203702</v>
+        <v>308.1463448879966</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>71.5</v>
+        <v>118</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41.56921731537675</v>
+        <v>36.36797598021241</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.52633904956159</v>
+        <v>31.12289122932142</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.557288776412477</v>
+        <v>0.2869888057149982</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.068102381376343</v>
+        <v>1.092828375226358</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6971</v>
+        <v>6895</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>424.7531116606714</v>
+        <v>307.3345920805156</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>27.8</v>
+        <v>163.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>55.79483146262889</v>
+        <v>53.31233002220708</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.66283544459023</v>
+        <v>21.11075115240364</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.858083079349517</v>
+        <v>0.3147952224205441</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1123674089866897</v>
+        <v>1.074708453036259</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8039</v>
+        <v>6951</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>422.5820057180303</v>
+        <v>292.3576454479485</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>145.5</v>
+        <v>78.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.23409038961434</v>
+        <v>40.69516708267099</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.53427725431343</v>
+        <v>24.68815243169518</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3415962345519952</v>
+        <v>0.2853365544659926</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1447782291629521</v>
+        <v>-0.4334547408420342</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7772</v>
+        <v>7818</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>418.625633689105</v>
+        <v>288.5344841143988</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>144</v>
+        <v>62.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>44.1685213886233</v>
+        <v>27.50266376966817</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10.22435008202764</v>
+        <v>50.19103836691456</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3020997329100194</v>
+        <v>0.9395044302101472</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.8611997538275933</v>
+        <v>1.241098162457014</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6861</v>
+        <v>8034</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>418.5707149562113</v>
+        <v>272.1354084794945</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>371</v>
+        <v>23.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.92903120599819</v>
+        <v>43.03488811885377</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.96251231812479</v>
+        <v>16.89827486202889</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9502964505439624</v>
+        <v>0.6295248263456898</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-6.015942501638275</v>
+        <v>-0.0594123123993094</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7805</v>
+        <v>7717</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>416.8359685124281</v>
+        <v>269.4345184423577</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>692</v>
+        <v>546</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>39.17108674388415</v>
+        <v>37.64929402475465</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>27.83507169194273</v>
+        <v>12.5629726545227</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3772593424062498</v>
+        <v>0.5055902727275075</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-10.50071878801823</v>
+        <v>-6.073009442390454</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7751</v>
+        <v>7728</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>400.4893416527729</v>
+        <v>254.1234264622786</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1485</v>
+        <v>712</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.73879082741485</v>
+        <v>46.56915603273989</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.76029042562354</v>
+        <v>11.30479248494925</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7203721557105931</v>
+        <v>0.4486642169033668</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.604911584916195</v>
+        <v>-2.864042052041732</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7714</v>
+        <v>6854</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>398.3246798935116</v>
+        <v>246.2806936379293</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>126.5</v>
+        <v>130</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.47950358467099</v>
+        <v>37.46377078754333</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.99844860213091</v>
+        <v>17.75644797894935</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2444004939081097</v>
+        <v>0.4745222422293887</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1495702199680841</v>
+        <v>-1.10182723464156</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7803</v>
+        <v>7703</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>394.5478031181166</v>
+        <v>234.6617517394446</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>23</v>
+        <v>206.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.34720391219354</v>
+        <v>50.71212334710267</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.7778037271467</v>
+        <v>13.1770001965346</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.395579889976011</v>
+        <v>1.294283970598995</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2960163535974192</v>
+        <v>1.048502731892831</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6983</v>
+        <v>7753</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>390.3143312976839</v>
+        <v>233.1102951008212</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>371</v>
+        <v>41.45</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.128016333813</v>
+        <v>43.59213538014333</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.79598919229082</v>
+        <v>18.17184544163588</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5544578149974652</v>
+        <v>1.209059933957144</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.203204793605927</v>
+        <v>-0.1374735794821692</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7765</v>
+        <v>8011</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>385.558341096051</v>
+        <v>231.425093457166</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.98958734022722</v>
+        <v>43.61134726953069</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.81012437211056</v>
+        <v>15.60635713233502</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.565550644220822</v>
+        <v>1.081687170842226</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.890893766107559</v>
+        <v>0.0225044735495425</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6910</v>
+        <v>7740</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>385.3276347974301</v>
+        <v>227.0243408173185</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.76201338977815</v>
+        <v>37.58636821071204</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.645476784193</v>
+        <v>12.28378018902849</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7604961104006213</v>
+        <v>1.273303130817899</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.05169079604524</v>
+        <v>-1.465190477920326</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8038</v>
+        <v>7402</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>384.0488199881506</v>
+        <v>223.3178479297891</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>40.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.18662900945512</v>
+        <v>35.84802274902216</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8.0961689896785</v>
+        <v>21.63865555503775</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7366652280783546</v>
+        <v>0.3500326557216506</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.000659126446641</v>
+        <v>0.197052910054448</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7738</v>
+        <v>6869</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>380.6069955485415</v>
+        <v>221.0578588269569</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>173.5</v>
+        <v>77.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.51655561813408</v>
+        <v>37.54669942288752</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.03488144174349</v>
+        <v>17.09386140956592</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.433349266732742</v>
+        <v>0.5969844484336049</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.8159764279742876</v>
+        <v>-0.5554975428574342</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6877</v>
+        <v>6863</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>367.06772344859</v>
+        <v>217.3891869784351</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>129.5</v>
+        <v>96.7</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33.95130760733625</v>
+        <v>39.24291189256029</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.13398514228543</v>
+        <v>22.3299081317623</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4374758432667606</v>
+        <v>0.7100180295008591</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-2.819663292549158</v>
+        <v>-1.224032182495849</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6936</v>
+        <v>8024</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>365.9805802280385</v>
+        <v>214.040549882721</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>33.4</v>
+        <v>12.25</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.36804892625419</v>
+        <v>43.97967728099772</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10.32599780301258</v>
+        <v>25.03633751999517</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1667866930241325</v>
+        <v>0.6922515339541176</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0389924543424297</v>
+        <v>-0.0041065270601328</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7747</v>
+        <v>6873</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>360.1818882143295</v>
+        <v>212.9863977965243</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>127.5</v>
+        <v>78.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.53694555246699</v>
+        <v>36.01092204818392</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7.093657299999292</v>
+        <v>15.26294323783395</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8143433928693629</v>
+        <v>0.6235223377065903</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0605464935010822</v>
+        <v>-1.300163283336426</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7822</v>
+        <v>6908</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>357.561088087943</v>
+        <v>208.5503163931757</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1165</v>
+        <v>38.75</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.21032987657522</v>
+        <v>45.40250165939788</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.27901936575351</v>
+        <v>11.41075806945577</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6843316997777271</v>
+        <v>0.1922540739247369</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>22.02124795936029</v>
+        <v>0.0647647497672366</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6903</v>
+        <v>6969</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>348.2842869429546</v>
+        <v>207.4098775934097</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>393</v>
+        <v>26.4</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.35929659966996</v>
+        <v>28.94631758683796</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.23688067048612</v>
+        <v>18.78932231489143</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3724515995218305</v>
+        <v>1.597149828285057</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.279158187854298</v>
+        <v>-0.0635648424914825</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6909</v>
+        <v>8045</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>347.6584620629205</v>
+        <v>197.6606829305441</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>50.9</v>
+        <v>61.1</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.73954751767833</v>
+        <v>38.74487848700784</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.38865010776942</v>
+        <v>13.32328936585558</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7663678731288543</v>
+        <v>0.2725900836570318</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2044289075605405</v>
+        <v>-0.2332224430520897</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6967</v>
+        <v>7704</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>346.5894321621794</v>
+        <v>188.6321964221916</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>71.3</v>
+        <v>58.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.9700152419006</v>
+        <v>41.84010800335959</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8.928712725860086</v>
+        <v>14.90113885444442</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2602919316211082</v>
+        <v>0.1357597391677019</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1683006970082186</v>
+        <v>-0.5259728096085712</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6958</v>
+        <v>6953</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>344.1690356020599</v>
+        <v>184.0883602398745</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>17.2</v>
+        <v>235</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.07003261120473</v>
+        <v>46.4719717946265</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.39264120614266</v>
+        <v>18.27817738800115</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5370574148110697</v>
+        <v>0.4867667511786044</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0892467358950773</v>
+        <v>-0.1654406088021778</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7730</v>
+        <v>6933</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>338.0968385043983</v>
+        <v>171.220104487116</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>180.5</v>
+        <v>157</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.29952964104086</v>
+        <v>46.24743421129599</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.23491152634267</v>
+        <v>18.25294111018007</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.922300514567449</v>
+        <v>0.3019218040847201</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-3.432634284807784</v>
+        <v>-1.261478005786743</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7750</v>
+        <v>6923</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>335.3054801246429</v>
+        <v>165.0435959654282</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>2370</v>
+        <v>77.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.85759176494079</v>
+        <v>44.82876750648217</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21.85240767154277</v>
+        <v>13.01325560470896</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7774772355713192</v>
+        <v>1.058506099523267</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-5.34502674523161</v>
+        <v>0.1262605051104299</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6994</v>
+        <v>7770</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>334.076048733258</v>
+        <v>142.328174709143</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>53.2</v>
+        <v>42.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>33.87052385392006</v>
+        <v>47.65506469006361</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.24864511816748</v>
+        <v>6.507822636975395</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8771037842306157</v>
+        <v>0.6733392374755787</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.543187694597757</v>
+        <v>-0.0183644532703243</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7744</v>
+        <v>6887</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>333.4268303378885</v>
+        <v>113.5286877461493</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>483</v>
+        <v>34.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.74504653589322</v>
+        <v>48.15888343486995</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.33824505713664</v>
+        <v>6.112213843935506</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2567902004705649</v>
+        <v>0.4849352815343896</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,2555 +4545,11 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.251186721368534</v>
+        <v>0.2116078256421266</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>6913</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>鴻呈</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>329.8392309500776</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>44.39803877474499</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>17.66333669696719</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>0.3239869523071693</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>-1.381291819109197</v>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>8047</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>星雲</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>323.7526437085389</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>50.78890181485215</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>7.174239871077289</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>0.0901396667932409</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N79" s="2" t="n">
-        <v>0.3760738437791017</v>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>7842</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>天能綠電</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>321.6545141031607</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>33.88043535380196</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>28.1770743341323</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>0.2151725515145541</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>0.5934244629452268</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>6918</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>愛派司</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>317.2624590010345</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>49.56692149742102</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>7.241251350388027</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>0.7810251334398018</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>0.0955111919222412</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>6855</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>數泓科</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>311.6636533119414</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>19.43593865023252</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>18.42662956889505</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>0.0002117119024431</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>-9.039665618385769</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>7820</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>立盈</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>308.1463448879966</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>36.36797606100925</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>31.12289122932142</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.2869888057149982</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>1.092828374673037</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>6895</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>宏碩系統</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>307.334592080516</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>53.3123301049121</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>21.11075117639435</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>0.3147952224205441</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>1.074708451032911</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>6865</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>偉康科技</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>303.4007617627669</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>48.7871025532549</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>22.6621221406735</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0.8402510411572196</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>0.5606657907077248</v>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>6951</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>青新-創</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>292.3576454479488</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>40.69516698218311</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>24.68815241389348</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0.2853365544659926</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>-0.4334547407657174</v>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>7839</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>達人網</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>282.391599698521</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>44.46958815191199</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>5.418680946704887</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>1.139159969852099</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-1.942152794471714</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>7547</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>碩網</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>281.5266511542634</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>40.73184011072361</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>14.70367946498528</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0.266980622962385</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>-0.0262310154827281</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>6914</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>阜爾運通</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>281.2540317743212</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>49.07612030943203</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>13.39366211479105</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>0.3357818081847211</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>0.313274388844122</v>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>8046</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>273.2245499881496</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>874</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>51.81213536359427</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>15.56943912016403</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0.9976836529635298</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>-1.925930552324632</v>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>8034</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>榮群</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>272.1354084794945</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>43.03488814888632</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>16.89827494923856</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0.6295248263456898</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-0.0594123124565502</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>7717</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>萊德光電-KY</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>269.4345184423577</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>546</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>37.64929402475465</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>12.5629726545227</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>0.5055902727275075</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>-6.073009442390454</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>7810</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>捷創科技</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>268.8060314074121</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>42.50703540058263</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>16.22151003914882</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0.2790767346079177</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>-1.527069311648167</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>7705</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>三商餐飲</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>264.9181480115171</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>31.85</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>51.53572730375429</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>16.52376371296965</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>0.4243713917879558</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>0.12417881255543</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>6937</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>天虹</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>263.6870141332407</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>45.67326866625337</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>14.43951115319942</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0.6385490452278444</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>-2.06692255987319</v>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>7728</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>光焱科技</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>254.1234264622786</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>712</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>46.56915600876054</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>11.30479248494925</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0.4486642169033668</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-2.864042052709588</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>6952</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>大武山</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>243.733290506953</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>36.05</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>40.88740131676055</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>19.3874682717287</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>1.448196908986835</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>0.0533885993808548</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>6955</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>邦睿生技-創</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>243.3007602543352</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>46.65242443624268</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>4.887507404065955</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0.4211144394544779</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>-0.7162923666297685</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>7791</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>皇家可口</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>239.3947920107147</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>38.02934765503297</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>22.05525715658517</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0.7804066367079792</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>-0.4312191611199875</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>7736</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>虎山</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>237.7674723319396</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>46.83897063867031</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>15.15136952242161</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0.4117905104221206</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0.2707879632609394</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>7823</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>奧義賽博-KY創</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>237.6313055838587</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>28.97164191193663</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>30.21055276497744</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0.3709250859441965</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-1.778712779714091</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>7753</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>星亞</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>233.1102951008212</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>41.45</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>43.5921353913617</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>18.17184542585836</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>1.209059933957144</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-0.1374735795107811</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>8011</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>台通</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>231.425093457166</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>43.61134721739128</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>15.60635710725926</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>1.081687170842226</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>0.0225044735113822</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>6885</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>全福生技</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>231.3222614784627</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>45.10201649050668</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>23.76266994016286</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0.4536327974654505</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>-0.1748762857487441</v>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>7740</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>熙特爾-創</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>227.0243408173185</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>37.58636821071204</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>12.2837801633292</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>1.273303130817899</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-1.465190478206528</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>6854</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>錼創科技-KY創</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>226.2806936379293</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>37.46377079627877</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>17.75644806792166</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0.4745222422293887</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>-1.101827234927727</v>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>7402</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>邑錡</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>223.3178479297889</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>35.84802275249965</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>21.63865558012292</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>0.3500326557216506</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>0.197052909672867</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>6869</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>雲豹能源</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>221.0578588269569</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>37.54669940169333</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>17.09386132617026</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0.5969844484336049</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>-0.5554975430482409</v>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>6988</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>威力暘-創</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>219.6203887967452</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>35.8600744004065</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>17.80053817318477</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>1.090330072198648</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>-0.145111425759738</v>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>7821</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>神數</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>219.5427124611598</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>41.6110610899239</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>17.24271872580923</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>0.5900710271395838</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>0.2618044235035608</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>6863</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>永道-KY</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>217.3891869784351</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>39.2429123348901</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>22.32990789483451</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>0.7100180295008591</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>-1.224032185643966</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>8024</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>佑華</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>214.040549882721</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>43.97967648820833</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>25.03633750539129</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>0.6922515339541176</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>-0.0041065270792128</v>
-      </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>6873</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>泓德能源</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>212.9863977965245</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>36.01092200417474</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>15.26294320663409</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>0.6235223377065903</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>-1.300163282859438</v>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>6908</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>宏碁遊戲-創</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>208.5503163931757</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>45.40250165939788</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>11.41075806945577</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0.1922540739247369</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>0.0647647497672366</v>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>6969</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>成信實業*-創</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>207.4098775934097</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>28.94631728072522</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>18.7893223951577</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>1.597149828285057</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-0.06356484251056051</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>8045</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>達運光電</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>197.6606829305442</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>38.7448783712183</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>13.32328932390218</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>0.2725900836570318</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>-0.2332224430902387</v>
-      </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>7704</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>明遠精密</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>188.6321964221916</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>41.84010810306393</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>14.90113887157918</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0.1357597391677019</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>-0.5259728098947642</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>7818</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>溢泰實業</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>178.5344841143988</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>27.50266402512828</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>50.1910381273519</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0.9395044302101472</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>1.241098161503041</v>
-      </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>6933</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>AMAX-KY</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>171.220104487116</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>46.24743419534982</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>18.25294113231463</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>0.3019218040847201</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-1.261478006454497</v>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>6923</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>中台</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>165.0435959654283</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>44.82876742419013</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>13.01325568252867</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>1.058506099523267</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>0.1262605050722706</v>
-      </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
           <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>8033</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>雷虎</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>155.0546495383514</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>129.5</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>44.01672328571166</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>7.590019994359082</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>0.9429034429924684</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>-0.2100879439455871</v>
-      </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>7770</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>君曜</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>142.328174709143</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>47.65506469968592</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>6.507822674386781</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0.6733392374755787</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>-0.0183644533275595</v>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>7703</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>銳澤</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>119.6617517394446</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>206.5</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>50.71212331687022</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>13.17700019292992</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>1.294283970598995</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>1.048502731511247</v>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>6887</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>寶綠特-KY</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>113.5286877461493</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>48.15888348046401</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>6.112213836994147</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>0.4849352815343896</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>0.2116078256612105</v>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>6953</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>家碩</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>69.0883602398745</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>235</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>46.47197187138737</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>18.27817742350318</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>0.4867667511786044</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>-0.1654406101377672</v>
-      </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq8_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7734</v>
+        <v>6949</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>987.9005258489774</v>
+        <v>1164.677388681171</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3615</v>
+        <v>911</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.5798119358565</v>
+        <v>77.27132684473099</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>22.31220982094863</v>
+        <v>27.86479833355272</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.034590332292282</v>
+        <v>3.067738868117068</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>10.95216455570819</v>
+        <v>27.44991224301391</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6862</v>
+        <v>6919</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>947.036135095865</v>
+        <v>1111.931730591041</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.97230924141576</v>
+        <v>63.83951119440479</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.06958126829194</v>
+        <v>15.54654663990211</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5108152053820165</v>
+        <v>7.250969212672749</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.525769846645995</v>
+        <v>1.442591461238072</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7715</v>
+        <v>7734</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>907.8519840893284</v>
+        <v>987.9005258489774</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32.4</v>
+        <v>3615</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>68.68571803996902</v>
+        <v>57.5798119358565</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28.00765992882794</v>
+        <v>22.31220982094863</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.385198408932845</v>
+        <v>1.034590332292282</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4463278126649261</v>
+        <v>10.95216455570819</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6916</v>
+        <v>6862</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>887.8572624005737</v>
+        <v>947.036135095865</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>22.3</v>
+        <v>227</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.14992095798303</v>
+        <v>61.97230924141576</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32.90052009897639</v>
+        <v>24.06958126829194</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8857262400573707</v>
+        <v>0.5108152053820165</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>2</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3362059025461689</v>
+        <v>1.525769846645995</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6859</v>
+        <v>7715</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>854.291958521682</v>
+        <v>907.8519840893284</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>139</v>
+        <v>32.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.54102514351862</v>
+        <v>68.68571803996902</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.76002931516605</v>
+        <v>28.00765992882794</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.029195852168194</v>
+        <v>4.385198408932845</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.8190734170096468</v>
+        <v>0.4463278126649261</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6962</v>
+        <v>6901</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>844.9932330493197</v>
+        <v>897.1329464591848</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>38.9</v>
+        <v>16.55</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.65203025088893</v>
+        <v>67.52038523238512</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.90328031894285</v>
+        <v>35.37127205999705</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.225427755355804</v>
+        <v>1.034459175954008</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1916046807249228</v>
+        <v>0.2082850481426372</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7795</v>
+        <v>6916</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>833.227694511472</v>
+        <v>887.8572624005737</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>410</v>
+        <v>22.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.14056071202359</v>
+        <v>66.14992095798303</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.19480516261392</v>
+        <v>32.90052009897639</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7919784478477986</v>
+        <v>0.8857262400573707</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.177973659795845</v>
+        <v>0.3362059025461689</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6944</v>
+        <v>8043</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>768.5683348281804</v>
+        <v>871.5462315557384</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1045</v>
+        <v>226.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>67.96657837597643</v>
+        <v>79.43040147009799</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>16.03118528692688</v>
+        <v>44.82124786731288</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8299085713804519</v>
+        <v>1.364997864833249</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>11.42030742116617</v>
+        <v>4.56000657972853</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7788</v>
+        <v>6859</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>758.1350586335629</v>
+        <v>854.291958521682</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>292</v>
+        <v>139</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>75.22909112239952</v>
+        <v>66.54102514351862</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.79815400685084</v>
+        <v>27.76002931516605</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.167671524725213</v>
+        <v>4.029195852168194</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>5.99656325006756</v>
+        <v>0.8190734170096468</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6907</v>
+        <v>6962</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>742.5878054950049</v>
+        <v>844.9932330493197</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>135.5</v>
+        <v>38.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.6381230859709</v>
+        <v>58.65203025088893</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.27335807284791</v>
+        <v>14.90328031894285</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3790718215480017</v>
+        <v>1.225427755355804</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.014432258892294</v>
+        <v>0.1916046807249228</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8032</v>
+        <v>7795</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>740.7355384641152</v>
+        <v>833.227694511472</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>47.6</v>
+        <v>410</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.44837833367268</v>
+        <v>57.14056071202359</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.05620439757024</v>
+        <v>13.19480516261392</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8181130490896236</v>
+        <v>0.7919784478477986</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1096101460042295</v>
+        <v>2.177973659795845</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8028</v>
+        <v>6944</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>733.7135128963364</v>
+        <v>768.5683348281804</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>311.5</v>
+        <v>1045</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>54.61450157490888</v>
+        <v>67.96657837597643</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.25572473915537</v>
+        <v>16.03118528692688</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7446180494833534</v>
+        <v>0.8299085713804519</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-5.252989334383123</v>
+        <v>11.42030742116617</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6922</v>
+        <v>7788</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>669.1119173573642</v>
+        <v>758.1350586335629</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>48.86222419665238</v>
+        <v>75.22909112239952</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.84170365551821</v>
+        <v>42.79815400685084</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3588929340142003</v>
+        <v>1.167671524725213</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.813926003701213</v>
+        <v>5.99656325006756</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8016</v>
+        <v>6907</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>654.4589501941159</v>
+        <v>742.5878054950049</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>300.5</v>
+        <v>135.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.05604690447676</v>
+        <v>51.6381230859709</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41.13419394963103</v>
+        <v>26.27335807284791</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.140336946547016</v>
+        <v>0.3790718215480017</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-2.875145279984213</v>
+        <v>-1.014432258892294</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7751</v>
+        <v>8032</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>615.4893416527729</v>
+        <v>740.7355384641152</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1485</v>
+        <v>47.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>43.73879081610948</v>
+        <v>64.44837833367268</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.76029034641975</v>
+        <v>29.05620439757024</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7203721557105931</v>
+        <v>0.8181130490896236</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>2.604911588445816</v>
+        <v>0.1096101460042295</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6894</v>
+        <v>8028</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>600.2503068362007</v>
+        <v>733.7135128963364</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>374.5</v>
+        <v>311.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.54489481769449</v>
+        <v>54.61450157490888</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.51425030627797</v>
+        <v>41.25572473915537</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6439822772194413</v>
+        <v>0.7446180494833534</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-2.007963300485517</v>
+        <v>-5.252989334383123</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8040</v>
+        <v>8044</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>599.5371487623396</v>
+        <v>729.186093263623</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>94.8</v>
+        <v>31.15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>49.06764876268207</v>
+        <v>60.94769992740687</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.27642056745299</v>
+        <v>25.31527379463125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2991987573095594</v>
+        <v>1.390114316782621</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.543443883278947</v>
+        <v>-0.2599045162276479</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6928</v>
+        <v>7827</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>597.7321188504669</v>
+        <v>694.7867890035916</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>47.95</v>
+        <v>164.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.56043439497374</v>
+        <v>61.60546667841415</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.65388862148918</v>
+        <v>25.67880571143168</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5807704309836691</v>
+        <v>0.4099837663020374</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3077237068065564</v>
+        <v>0.944323625013518</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7769</v>
+        <v>6861</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>577.3663924961251</v>
+        <v>693.5707149562113</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6975</v>
+        <v>371</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.92241458741501</v>
+        <v>53.9290312041619</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.1350989544269</v>
+        <v>27.9625123238291</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.756544484813861</v>
+        <v>0.9502964505439624</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-111.8347939315777</v>
+        <v>-6.015942501428464</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7786</v>
+        <v>7722</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>569.9334135486423</v>
+        <v>692.5074734046849</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>130</v>
+        <v>328</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.89132874301954</v>
+        <v>58.07711001546964</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.744046685636</v>
+        <v>37.02612462088066</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.565886563057089</v>
+        <v>0.8867378661926932</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.686091075600813</v>
+        <v>4.110925334883651</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6899</v>
+        <v>6922</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>565.7639725880447</v>
+        <v>669.1119173573642</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>60.8</v>
+        <v>186</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>49.73096334190152</v>
+        <v>48.86222419665238</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.81735437142484</v>
+        <v>21.84170365551821</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2232148690362529</v>
+        <v>0.3588929340142003</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.5246901299096405</v>
+        <v>-1.813926003701213</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7822</v>
+        <v>8016</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>557.5610880879431</v>
+        <v>654.4589501941159</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1165</v>
+        <v>300.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.21032986535594</v>
+        <v>59.05604690447676</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.27901928846354</v>
+        <v>41.13419394963103</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6843316997777271</v>
+        <v>1.140336946547016</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>22.02124796145895</v>
+        <v>-2.875145279984213</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7749</v>
+        <v>7799</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>556.8429773371901</v>
+        <v>649.5494983147198</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>484.5</v>
+        <v>362</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.23088328915198</v>
+        <v>55.43506629945007</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.57667571278461</v>
+        <v>28.37383409896165</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5053467570796943</v>
+        <v>1.720813624847022</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-2.676221013404523</v>
+        <v>2.994396584535662</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7772</v>
+        <v>6870</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>528.625633689105</v>
+        <v>637.7234640164453</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>144</v>
+        <v>285.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>44.1685213886233</v>
+        <v>58.86224372002275</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.22435008202764</v>
+        <v>31.23350784427048</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3020997329100194</v>
+        <v>0.507219104700247</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.8611997538275933</v>
+        <v>-3.417477447474695</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6996</v>
+        <v>7750</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>519.9140229928366</v>
+        <v>620.3054801246429</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>194</v>
+        <v>2370</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.97868774095526</v>
+        <v>53.8575917759437</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.11084057336648</v>
+        <v>21.85240765149323</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.365468008158648</v>
+        <v>0.7774772355713192</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.6636070429471093</v>
+        <v>-5.34502674246481</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7631</v>
+        <v>7751</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>518.6204920518406</v>
+        <v>615.4893416527729</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>131.5</v>
+        <v>1485</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.99289637569444</v>
+        <v>43.73879081610948</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>11.38796907973604</v>
+        <v>17.76029034641975</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8190607558399428</v>
+        <v>0.7203721557105931</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.383752150672917</v>
+        <v>2.604911588445816</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6909</v>
+        <v>6957</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>517.6584620629204</v>
+        <v>610.7595085314617</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>50.9</v>
+        <v>189.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.73954754873523</v>
+        <v>64.50327980880631</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19.38865011854004</v>
+        <v>29.28546014314312</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7663678731288543</v>
+        <v>0.3971731357373318</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2044289075414611</v>
+        <v>0.2316673557464597</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8038</v>
+        <v>6894</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>494.0488199881506</v>
+        <v>600.2503068362007</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>40.8</v>
+        <v>374.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>47.18662902348751</v>
+        <v>54.54489481769449</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>8.096168990550082</v>
+        <v>22.51425030627797</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7366652280783546</v>
+        <v>0.6439822772194413</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0006591264180267</v>
+        <v>-2.007963300485517</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7768</v>
+        <v>8040</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>492.4421157828301</v>
+        <v>599.5371487623396</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>373</v>
+        <v>94.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.14416201608335</v>
+        <v>49.06764876268207</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.53369312403196</v>
+        <v>33.27642056745299</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.417429141261481</v>
+        <v>0.2991987573095594</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-2.669767958587202</v>
+        <v>-2.543443883278947</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7792</v>
+        <v>6928</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>488.5625833464821</v>
+        <v>597.7321188504669</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>261</v>
+        <v>47.95</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>41.09836395617206</v>
+        <v>55.56043439497374</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.59391806353022</v>
+        <v>18.65388862148918</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5250550882829239</v>
+        <v>0.5807704309836691</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.413962657483534</v>
+        <v>0.3077237068065564</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7556</v>
+        <v>7769</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>480.9658022500324</v>
+        <v>577.3663924961251</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>275</v>
+        <v>6975</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.43781068077278</v>
+        <v>49.92241458741501</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14.35387541298493</v>
+        <v>26.1350989544269</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4499932620181174</v>
+        <v>1.756544484813861</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.187139003385701</v>
+        <v>-111.8347939315777</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7711</v>
+        <v>7760</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>468.8680222571436</v>
+        <v>574.7067073967402</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>364.5</v>
+        <v>33.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46.54543546892593</v>
+        <v>56.39866270237481</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15.20476050171334</v>
+        <v>51.07186400041447</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3195542206711939</v>
+        <v>1.239237223997006</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-3.400538332695817</v>
+        <v>0.2831274418470129</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8046</v>
+        <v>7786</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>453.2247808941766</v>
+        <v>569.9334135486423</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>874</v>
+        <v>130</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.81213536549598</v>
+        <v>56.89132874301954</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.56943907480537</v>
+        <v>21.744046685636</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9977370179756412</v>
+        <v>0.565886563057089</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.925930552324632</v>
+        <v>1.686091075600813</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6921</v>
+        <v>6899</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>448.767736203702</v>
+        <v>565.7639725880447</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>71.5</v>
+        <v>60.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>41.56921731537675</v>
+        <v>49.73096334190152</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.52633904956159</v>
+        <v>21.81735437142484</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.557288776412477</v>
+        <v>0.2232148690362529</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.068102381376343</v>
+        <v>-0.5246901299096405</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6994</v>
+        <v>6934</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>431.1890524576613</v>
+        <v>562.5163829342484</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>53.2</v>
+        <v>71.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>33.87052383644441</v>
+        <v>45.29458260202556</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.24864514962118</v>
+        <v>33.75840066763514</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.917830044310564</v>
+        <v>2.725741867851815</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>2</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.5431876939490561</v>
+        <v>0.0976017676478364</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6971</v>
+        <v>7822</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>424.7531116606714</v>
+        <v>557.5610880879431</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27.8</v>
+        <v>1165</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.79483099667572</v>
+        <v>52.21032986535594</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.66283544547555</v>
+        <v>15.27901928846354</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6.858083079349517</v>
+        <v>0.6843316997777271</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1123674090439286</v>
+        <v>22.02124796145895</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8039</v>
+        <v>7749</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>422.5820057180303</v>
+        <v>556.8429773371901</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>145.5</v>
+        <v>484.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.23409039173137</v>
+        <v>49.23088328915198</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.53427725444031</v>
+        <v>24.57667571278461</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3415962345519952</v>
+        <v>0.5053467570796943</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1447782291343317</v>
+        <v>-2.676221013404523</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7730</v>
+        <v>6997</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>413.0968385043983</v>
+        <v>551.5711108272301</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>180.5</v>
+        <v>75</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45.29952967867194</v>
+        <v>51.95485878169522</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.23491138656478</v>
+        <v>9.024951418898571</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.922300514567449</v>
+        <v>0.7031895506032781</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.432634284979499</v>
+        <v>0.2136492439612949</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6983</v>
+        <v>6965</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>410.3143312976839</v>
+        <v>532.5290407408071</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.12801635364296</v>
+        <v>55.88810589538004</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14.79598920336904</v>
+        <v>21.91330590412771</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5544578149974652</v>
+        <v>0.668623395266623</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.203204793319742</v>
+        <v>0.3657690354614468</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6937</v>
+        <v>7772</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>373.6870141332407</v>
+        <v>528.625633689105</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>279.5</v>
+        <v>144</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.67326867895551</v>
+        <v>44.1685213886233</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.43951114899719</v>
+        <v>10.22435008202764</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6385490452278444</v>
+        <v>0.3020997329100194</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.066922559587018</v>
+        <v>-0.8611997538275933</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6877</v>
+        <v>6996</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>367.0677234485899</v>
+        <v>519.9140229928366</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>129.5</v>
+        <v>194</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>33.95130760733625</v>
+        <v>52.97868774095526</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.13398511705011</v>
+        <v>26.11084057336648</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4374758432667606</v>
+        <v>0.365468008158648</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-2.819663292358374</v>
+        <v>-0.6636070429471093</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6903</v>
+        <v>7631</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>348.2842869429546</v>
+        <v>518.6204920518406</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>393</v>
+        <v>131.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.35929659966996</v>
+        <v>52.99289637569444</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.23688062210877</v>
+        <v>11.38796907973604</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3724515995218305</v>
+        <v>0.8190607558399428</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.279158187281936</v>
+        <v>2.383752150672917</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6967</v>
+        <v>6909</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>346.5894321621794</v>
+        <v>517.6584620629204</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>71.3</v>
+        <v>50.9</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.97001517402723</v>
+        <v>52.73954754873523</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8.928712743276755</v>
+        <v>19.38865011854004</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2602919316211082</v>
+        <v>0.7663678731288543</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>1</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1683006971226828</v>
+        <v>0.2044289075414611</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7810</v>
+        <v>7803</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>343.8060314074121</v>
+        <v>504.5478031181166</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>42.50703540058263</v>
+        <v>39.34720395375458</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.22151006662083</v>
+        <v>20.7778037271467</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2790767346079177</v>
+        <v>0.395579889976011</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.527069311648167</v>
+        <v>0.296016353482941</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7842</v>
+        <v>6931</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>341.6545141031607</v>
+        <v>495.3043685114233</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>101</v>
+        <v>40.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.88043535380196</v>
+        <v>40.51977923162121</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>28.1770743341323</v>
+        <v>25.33506415003443</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2151725515145541</v>
+        <v>0.9980024173154238</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5934244629452268</v>
+        <v>0.311145508121551</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7744</v>
+        <v>8038</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>333.4268303378885</v>
+        <v>494.0488199881506</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>483</v>
+        <v>40.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.7450465378931</v>
+        <v>47.18662902348751</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.33824504622382</v>
+        <v>8.096168990550082</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2567902004705649</v>
+        <v>0.7366652280783546</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.251186721463942</v>
+        <v>-0.0006591264180267</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6913</v>
+        <v>7768</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>329.8392309500776</v>
+        <v>492.4421157828301</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>126</v>
+        <v>373</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.39803875227739</v>
+        <v>44.14416201608335</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.66333668889722</v>
+        <v>16.53369312403196</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3239869523071693</v>
+        <v>0.417429141261481</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.38129181853682</v>
+        <v>-2.669767958587202</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6855</v>
+        <v>7805</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>311.6636533119414</v>
+        <v>491.8359685124281</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>19.43593864093283</v>
+        <v>39.1710867334784</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.42662956809367</v>
+        <v>27.8350716466441</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.0002117119024431</v>
+        <v>0.3772593424062498</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-9.039665618099562</v>
+        <v>-10.500718785538</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7820</v>
+        <v>7792</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>308.1463448879966</v>
+        <v>488.5625833464821</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>36.36797598021241</v>
+        <v>41.09836395617206</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.12289122932142</v>
+        <v>22.59391806353022</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2869888057149982</v>
+        <v>0.5250550882829239</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.092828375226358</v>
+        <v>0.413962657483534</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6895</v>
+        <v>7721</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>307.3345920805156</v>
+        <v>487.5897910431749</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>163.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.31233002220708</v>
+        <v>47.22137647538585</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.11075115240364</v>
+        <v>16.22118581096243</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3147952224205441</v>
+        <v>0.6095267323383532</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.074708453036259</v>
+        <v>-0.2197653519490582</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6951</v>
+        <v>7556</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>292.3576454479485</v>
+        <v>480.9658022500324</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>78.8</v>
+        <v>275</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>40.69516708267099</v>
+        <v>50.43781068077278</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.68815243169518</v>
+        <v>14.35387541298493</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2853365544659926</v>
+        <v>0.4499932620181174</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.4334547408420342</v>
+        <v>-1.187139003385701</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7818</v>
+        <v>6925</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>288.5344841143988</v>
+        <v>472.8038711250216</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>62.2</v>
+        <v>63.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>27.50266376966817</v>
+        <v>46.36348139923352</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>50.19103836691456</v>
+        <v>21.56178230216404</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9395044302101472</v>
+        <v>0.2462700124787925</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.241098162457014</v>
+        <v>-0.5308472308139262</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8034</v>
+        <v>7711</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>272.1354084794945</v>
+        <v>468.8680222571436</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>23.4</v>
+        <v>364.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.03488811885377</v>
+        <v>46.54543546892593</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.89827486202889</v>
+        <v>15.20476050171334</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6295248263456898</v>
+        <v>0.3195542206711939</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0594123123993094</v>
+        <v>-3.400538332695817</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7717</v>
+        <v>7780</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>269.4345184423577</v>
+        <v>461.96783481067</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>546</v>
+        <v>19.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>37.64929402475465</v>
+        <v>57.75741441703657</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12.5629726545227</v>
+        <v>20.59962245454168</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5055902727275075</v>
+        <v>1.330622072181422</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-6.073009442390454</v>
+        <v>0.2412769932200579</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7728</v>
+        <v>7732</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>254.1234264622786</v>
+        <v>454.2812256037837</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>712</v>
+        <v>36</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.56915603273989</v>
+        <v>51.93558382286199</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.30479248494925</v>
+        <v>17.28765614224055</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4486642169033668</v>
+        <v>1.749934377460845</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.864042052041732</v>
+        <v>-1.309985943401701</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6854</v>
+        <v>8046</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>246.2806936379293</v>
+        <v>453.2247808941766</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>130</v>
+        <v>874</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>37.46377078754333</v>
+        <v>51.81213536549598</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.75644797894935</v>
+        <v>15.56943907480537</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4745222422293887</v>
+        <v>0.9977370179756412</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.10182723464156</v>
+        <v>-1.925930552324632</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7703</v>
+        <v>6921</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>234.6617517394446</v>
+        <v>448.767736203702</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>206.5</v>
+        <v>71.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.71212334710267</v>
+        <v>41.56921731537675</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.1770001965346</v>
+        <v>27.52633904956159</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.294283970598995</v>
+        <v>1.557288776412477</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.048502731892831</v>
+        <v>0.068102381376343</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7753</v>
+        <v>6906</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>233.1102951008212</v>
+        <v>442.7557583140691</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>41.45</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.59213538014333</v>
+        <v>53.83922896769034</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.17184544163588</v>
+        <v>28.87745177098057</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.209059933957144</v>
+        <v>0.6413431135715212</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1374735794821692</v>
+        <v>-2.135554960488712</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8011</v>
+        <v>6902</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>231.425093457166</v>
+        <v>431.4450953227969</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.61134726953069</v>
+        <v>53.18357563282667</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.60635713233502</v>
+        <v>30.66984233889536</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.081687170842226</v>
+        <v>0.3755523079881189</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0225044735495425</v>
+        <v>-2.905209917093768</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7740</v>
+        <v>6994</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>227.0243408173185</v>
+        <v>431.1890524576613</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>156</v>
+        <v>53.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>37.58636821071204</v>
+        <v>33.87052383644441</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.28378018902849</v>
+        <v>18.24864514962118</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.273303130817899</v>
+        <v>1.917830044310564</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.465190477920326</v>
+        <v>-0.5431876939490561</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7402</v>
+        <v>6971</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>223.3178479297891</v>
+        <v>424.7531116606714</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>27.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>35.84802274902216</v>
+        <v>55.79483099667572</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.63865555503775</v>
+        <v>18.66283544547555</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3500326557216506</v>
+        <v>6.858083079349517</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.197052910054448</v>
+        <v>0.1123674090439286</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6869</v>
+        <v>8039</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>221.0578588269569</v>
+        <v>422.5820057180303</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>77.3</v>
+        <v>145.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>37.54669942288752</v>
+        <v>52.23409039173137</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.09386140956592</v>
+        <v>22.53427725444031</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5969844484336049</v>
+        <v>0.3415962345519952</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.5554975428574342</v>
+        <v>-0.1447782291343317</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6863</v>
+        <v>6958</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>217.3891869784351</v>
+        <v>419.1690356020599</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>96.7</v>
+        <v>17.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>39.24291189256029</v>
+        <v>48.07003262068263</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.3299081317623</v>
+        <v>19.39264124435405</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7100180295008591</v>
+        <v>0.5370574148110697</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>1</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.224032182495849</v>
+        <v>0.0892467359046137</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8024</v>
+        <v>7714</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>214.040549882721</v>
+        <v>418.3246798935121</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.25</v>
+        <v>126.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.97967728099772</v>
+        <v>47.47950360386603</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.03633751999517</v>
+        <v>22.99844868875508</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6922515339541176</v>
+        <v>0.2444004939081097</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0041065270601328</v>
+        <v>-0.1495702178693315</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6873</v>
+        <v>7730</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>212.9863977965243</v>
+        <v>413.0968385043983</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>78.8</v>
+        <v>180.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>36.01092204818392</v>
+        <v>45.29952967867194</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.26294323783395</v>
+        <v>18.23491138656478</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6235223377065903</v>
+        <v>0.922300514567449</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.300163283336426</v>
+        <v>-3.432634284979499</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6908</v>
+        <v>6983</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>208.5503163931757</v>
+        <v>410.3143312976839</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>38.75</v>
+        <v>371</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.40250165939788</v>
+        <v>49.12801635364296</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.41075806945577</v>
+        <v>14.79598920336904</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.1922540739247369</v>
+        <v>0.5544578149974652</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0647647497672366</v>
+        <v>1.203204793319742</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6969</v>
+        <v>7765</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>207.4098775934097</v>
+        <v>385.5583410960519</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>26.4</v>
+        <v>238</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>28.94631758683796</v>
+        <v>42.98958724339482</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.78932231489143</v>
+        <v>28.81012445789857</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.597149828285057</v>
+        <v>1.565550644220822</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0635648424914825</v>
+        <v>-1.890893763818011</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8045</v>
+        <v>6910</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>197.6606829305441</v>
+        <v>385.3276347974301</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>61.1</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38.74487848700784</v>
+        <v>44.76201338977815</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.32328936585558</v>
+        <v>12.64547679212826</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2725900836570318</v>
+        <v>0.7604961104006213</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.2332224430520897</v>
+        <v>-0.0516907960929359</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7704</v>
+        <v>7738</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>188.6321964221916</v>
+        <v>380.6069955485415</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>58.2</v>
+        <v>173.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.84010800335959</v>
+        <v>54.51655563210503</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.90113885444442</v>
+        <v>23.03488143317139</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1357597391677019</v>
+        <v>1.433349266732742</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5259728096085712</v>
+        <v>0.8159764278788875</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6953</v>
+        <v>7705</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>184.0883602398745</v>
+        <v>374.9181480115176</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>235</v>
+        <v>31.85</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.4719717946265</v>
+        <v>51.53572719282312</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.27817738800115</v>
+        <v>16.52376370022369</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4867667511786044</v>
+        <v>0.4243713917879558</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1654406088021778</v>
+        <v>0.1241788126508304</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6933</v>
+        <v>6937</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>171.220104487116</v>
+        <v>373.6870141332407</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>157</v>
+        <v>279.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.24743421129599</v>
+        <v>45.67326867895551</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.25294111018007</v>
+        <v>14.43951114899719</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3019218040847201</v>
+        <v>0.6385490452278444</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.261478005786743</v>
+        <v>-2.066922559587018</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6923</v>
+        <v>6877</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>165.0435959654282</v>
+        <v>367.0677234485899</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>77.7</v>
+        <v>129.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.82876750648217</v>
+        <v>33.95130760733625</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.01325560470896</v>
+        <v>22.13398511705011</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.058506099523267</v>
+        <v>0.4374758432667606</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1262605051104299</v>
+        <v>-2.819663292358374</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7770</v>
+        <v>6936</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>142.328174709143</v>
+        <v>365.9805802280383</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>42.2</v>
+        <v>33.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.65506469006361</v>
+        <v>46.36804824345772</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6.507822636975395</v>
+        <v>10.32599781705518</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6733392374755787</v>
+        <v>0.1667866930241325</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,62 +4492,2606 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0183644532703243</v>
+        <v>0.0389924540466896</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
+        <v>7747</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>昕奇雲端</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>360.1818882143297</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>51.53694553429468</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>7.093657481048218</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.8143433928693629</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0.0605464937872808</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>6903</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>巨漢</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>348.2842869429546</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>50.35929659966996</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>15.23688062210877</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.3724515995218305</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-1.279158187281936</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>7736</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>虎山</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>347.7674723319399</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>46.83897063867031</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>15.1513698365186</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.4117905104221206</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0.2707879634517375</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>6967</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>汎瑋材料</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>346.5894321621794</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>48.97001517402723</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>8.928712743276755</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.2602919316211082</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.1683006971226828</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>7810</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>捷創科技</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>343.8060314074121</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>42.50703540058263</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>16.22151006662083</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.2790767346079177</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-1.527069311648167</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>7842</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>天能綠電</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>341.6545141031607</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>33.88043535380196</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>28.1770743341323</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.2151725515145541</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.5934244629452268</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6918</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>愛派司</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>337.2624590010345</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>49.56692149742102</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>7.241251316517233</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.7810251334398018</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.0955111920176312</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>7744</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>崴寶</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>333.4268303378885</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>46.7450465378931</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>13.33824504622382</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.2567902004705649</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>1.251186721463942</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6913</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>鴻呈</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>329.8392309500776</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>44.39803875227739</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>17.66333668889722</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.3239869523071693</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-1.38129181853682</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>8047</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>星雲</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>323.7526437085389</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>50.78890181272715</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>7.174239850209416</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.0901396667932409</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.376073843836342</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6855</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>數泓科</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>311.6636533119414</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>19.43593864093283</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>18.42662956809367</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.0002117119024431</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-9.039665618099562</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>7820</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>立盈</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>308.1463448879966</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>36.36797598021241</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>31.12289122932142</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.2869888057149982</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>1.092828375226358</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6895</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>宏碩系統</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>307.3345920805156</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>53.31233002220708</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>21.11075115240364</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.3147952224205441</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>1.074708453036259</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6865</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>偉康科技</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>303.400761762767</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>48.78710263657459</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>22.66212205997061</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.8402510411572196</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.5606657905169277</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6951</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>青新-創</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>292.3576454479485</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>40.69516708267099</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>24.68815243169518</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.2853365544659926</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-0.4334547408420342</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>7818</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>溢泰實業</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>288.5344841143988</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>27.50266376966817</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>50.19103836691456</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.9395044302101472</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>1.241098162457014</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>7839</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>達人網</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>282.391599698521</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>44.46958815191199</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>5.418680946704887</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>1.139159969852099</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-1.942152794471714</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>7547</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>碩網</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>281.5266511542634</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>40.73184036291254</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>14.70367954350017</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.266980622962385</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.0262310149485012</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6914</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>阜爾運通</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>281.2540317743212</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>49.07612040716251</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>13.39366214310988</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.3357818081847211</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.3132743887487434</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>8034</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>榮群</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>272.1354084794945</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>43.03488811885377</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>16.89827486202889</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.6295248263456898</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.0594123123993094</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>7717</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>萊德光電-KY</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>269.4345184423577</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>546</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>37.64929402475465</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>12.5629726545227</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.5055902727275075</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-6.073009442390454</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>7728</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>光焱科技</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>254.1234264622786</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>712</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>46.56915603273989</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>11.30479248494925</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.4486642169033668</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-2.864042052041732</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6854</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>錼創科技-KY創</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>246.2806936379293</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>37.46377078754333</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>17.75644797894935</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.4745222422293887</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-1.10182723464156</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6952</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>大武山</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>243.733290506953</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>40.88740121429986</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>19.38746822952384</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.448196908986835</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.0533885994380918</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6955</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>邦睿生技-創</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>243.3007602543351</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>46.65242445431097</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>4.887507406533943</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.4211144394544779</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.7162923669159635</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>7791</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>皇家可口</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>239.3947920107147</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>38.02934756350395</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>22.05525721029186</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.7804066367079792</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.4312191610245887</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>7823</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>奧義賽博-KY創</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>237.6313055838587</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>28.97164191193663</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>30.21055276497744</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.3709250859441965</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-1.778712779714091</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>7703</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>銳澤</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>234.6617517394446</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>50.71212334710267</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>13.1770001965346</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>1.294283970598995</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>1.048502731892831</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>233.1102951008212</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>43.59213538014333</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>18.17184544163588</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.209059933957144</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.1374735794821692</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>8011</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>台通</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>231.425093457166</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>43.61134726953069</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>15.60635713233502</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.081687170842226</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0.0225044735495425</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6885</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>全福生技</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>231.3222614784628</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>45.10201649933781</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>23.76266994016286</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.4536327974654505</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.1748762856342685</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>7740</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>熙特爾-創</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>227.0243408173185</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>37.58636821071204</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>12.28378018902849</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>1.273303130817899</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-1.465190477920326</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>邑錡</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>223.3178479297891</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>35.84802274902216</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>21.63865555503775</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.3500326557216506</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.197052910054448</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6869</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>雲豹能源</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>221.0578588269569</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>37.54669942288752</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>17.09386140956592</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.5969844484336049</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-0.5554975428574342</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6988</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>威力暘-創</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>219.6203887967452</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>35.86007073644006</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>17.80053813461951</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1.090330072198648</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.1451114255880232</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>7821</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>神數</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>219.5427124611598</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>41.61106113030817</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>17.24271872580923</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.5900710271395838</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.2618044236180346</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6863</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>永道-KY</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>217.3891869784351</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>39.24291189256029</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3299081317623</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.7100180295008591</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-1.224032182495849</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>8024</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>佑華</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>214.040549882721</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>43.97967728099772</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>25.03633751999517</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.6922515339541176</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.0041065270601328</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6873</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>泓德能源</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>212.9863977965243</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>36.01092204818392</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>15.26294323783395</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.6235223377065903</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-1.300163283336426</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6908</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>宏碁遊戲-創</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>208.5503163931757</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>45.40250165939788</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>11.41075806945577</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.1922540739247369</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0647647497672366</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6969</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>成信實業*-創</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>207.4098775934097</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>28.94631758683796</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>18.78932231489143</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1.597149828285057</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0635648424914825</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>8045</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>達運光電</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>197.6606829305441</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>38.74487848700784</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>13.32328936585558</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.2725900836570318</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.2332224430520897</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>7704</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>明遠精密</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>188.6321964221916</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>41.84010800335959</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>14.90113885444442</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.1357597391677019</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.5259728096085712</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>8033</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>雷虎</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>185.0546495383512</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>44.0167232819836</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>7.590019902729987</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.9429034429924684</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-0.2100879434685909</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6953</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>家碩</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>184.0883602398745</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>46.4719717946265</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>18.27817738800115</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.4867667511786044</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.1654406088021778</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>AMAX-KY</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>171.220104487116</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>46.24743421129599</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>18.25294111018007</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.3019218040847201</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-1.261478005786743</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>6923</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>中台</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>165.0435959654282</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>44.82876750648217</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>13.01325560470896</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.058506099523267</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.1262605051104299</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>君曜</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>142.328174709143</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>47.65506469006361</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>6.507822636975395</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.6733392374755787</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.0183644532703243</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
         <v>6887</v>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>寶綠特-KY</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D77" s="2" t="n">
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
         <v>113.5286877461493</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E125" s="2" t="n">
         <v>34.2</v>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H77" s="2" t="n">
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
         <v>48.15888343486995</v>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I125" s="2" t="n">
         <v>6.112213843935506</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="J125" s="2" t="n">
         <v>0.4849352815343896</v>
       </c>
-      <c r="K77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N77" s="2" t="n">
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
         <v>0.2116078256421266</v>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O125" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
